--- a/data/xlsx/c01_edge.xlsx
+++ b/data/xlsx/c01_edge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/dlt-pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/dlt-pipeline/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3802A958-1A2E-424A-8E4B-2610A5537D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED2108-5EBD-F442-8907-2E9ECFD51903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="600" windowWidth="25440" windowHeight="15800"/>
+    <workbookView xWindow="400" yWindow="600" windowWidth="25440" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="c01_edge" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>contact</t>
   </si>
@@ -158,12 +158,30 @@
   </si>
   <si>
     <t>Text none/Null in date</t>
+  </si>
+  <si>
+    <t>some</t>
+  </si>
+  <si>
+    <t>extraneous</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>not</t>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>blah</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -998,97 +1016,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45351</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
@@ -1096,123 +1114,175 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>20240230</v>
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1">
         <v>45351</v>
       </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7">
+        <v>20240230</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1">
+        <v>45351</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9">
         <f>86-0</f>
         <v>86</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F9" t="s">
         <v>33</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>15012345678</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>1501234567890</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E10" s="1">
         <v>45327</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F10" s="1">
         <v>45414</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F11" t="s">
         <v>40</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G11" t="s">
         <v>41</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H11" t="s">
         <v>9</v>
       </c>
     </row>
